--- a/data_extactor/batch_10_fa/trimmed/batch_0049_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0049_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | علوم تجربی | ریاضیات | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | علوم | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زیست‌شناسی | فیزیک | پزشکی و دندان‌پزشکی | شیمی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | فیزیک | پزشکی و دندان‌پزشکی | شیمی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | درک کتبی | مرتب‌سازی اطلاعات | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان قلب و عروق | سونوگرافیست‌های تشخیصی پزشکی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دزیمتریست‌های پزشکی | تکنسین‌های پایش هسته‌ای | پرتودرمانگران (رادیوتراپیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری</t>
+          <t>کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دزیمتریست‌های پزشکی | تکنسین‌های پایش و حفاظت پرتوی | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | امور اداری و دفتری | ایمنی و امنیت عمومی | فیزیک</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | رایانه و الکترونیک | اداری | ایمنی و امنیت عمومی | فیزیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | بیان شفاهی | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان قلب و عروق | سونوگرافیست‌های تشخیصی پزشکی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان و تکنسین‌های پزشکی هسته‌ای | پرتودرمانگران (رادیوتراپیست‌ها) | رادیولوژیست‌ها (متخصصان رادیولوژی) | تکنسین‌های اتاق عمل (تکنسین‌های جراحی)</t>
+          <t>کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان و تکنسین‌های پزشکی هسته‌ای | پرتودرمانگران / کارشناسان رادیوتراپی | متخصصان رادیولوژی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فیزیک | رایانه و الکترونیک | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | زیست‌شناسی</t>
+          <t>خدمات مشتری و شخصی | فیزیک | رایانه و الکترونیک | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | درک کتبی | حساسیت به مسئله | استدلال قیاسی | دقت کنترل</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | حساسیت به مسئله | استدلال قیاسی | دقت کنترل</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان قلب و عروق | سونوگرافیست‌های تشخیصی پزشکی | دزیمتریست‌های پزشکی | کارشناسان و تکنسین‌های پزشکی هسته‌ای | پرتودرمانگران (رادیوتراپیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | رادیولوژیست‌ها (متخصصان رادیولوژی)</t>
+          <t>کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | دزیمتریست‌های پزشکی | کارشناسان و تکنسین‌های پزشکی هسته‌ای | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>محیط توسعه Eclipse IDE | سیستم‌های Epic Systems | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری بیماری‌ها و اقدامات پزشکی</t>
+          <t>محیط توسعه Eclipse IDE | سیستم‌های Epic Systems | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات | نظارت | علوم تجربی | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | درک شفاهی | حساسیت به مسئله | دید نزدیک | استدلال ریاضی</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان زیستی و مهندسان پزشکی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های پایش هسته‌ای | پرتودرمانگران (رادیوتراپیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | رادیولوژیست‌ها (متخصصان رادیولوژی)</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | روان‌شناسی | حمل‌ونقل و ترابری | درمان و مشاوره‌گری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | روان‌شناسی | حمل و نقل | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | زمان واکنش</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | تکنسین‌ها و کارشناسان قلب و عروق | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | پرستاران رسمی | درمانگران تنفسی</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | کارشناسان و تکنسین‌های قلب و عروق | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | روان‌شناسی | حمل‌ونقل و ترابری | درمان و مشاوره‌گری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | روان‌شناسی | حمل و نقل | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | زمان واکنش</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | تکنسین‌ها و کارشناسان قلب و عروق | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران رسمی | درمانگران تنفسی</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | ریاضیات | ایمنی و امنیت عمومی | تولید مواد غذایی | تولید و فراوری</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | ریاضیات | ایمنی و امنیت عمومی | تولید مواد غذایی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | دید نزدیک | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>آشپزهای سازمانی، بیمارستانی و سلف‌سرویس | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | هماهنگ‌کنندگان تناسب اندام و سلامت | دانشمندان و فناوران صنایع غذایی | مدیران خدمات پذیرایی و غذا | کارشناسان آموزش و ارتقای سلامت | بهیاران و کمک‌پرستاران دارای مجوز</t>
+          <t>آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | متخصصان و کارشناسان علوم و صنایع غذایی | مدیران خدمات پذیرایی و غذا و نوشیدنی | کارشناسان آموزش بهداشت و ارتقای سلامت | بهیاران و کمک‌پرستاران دارای مجوز</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | ریاضیات</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | ریاضیات | رایانه و الکترونیک | حقوق و مقررات دولتی | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | ریاضیات | رایانه و الکترونیک | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | مرتب‌سازی اطلاعات | حساسیت به مسئله | چابکی انگشتان</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | ترتیب‌دهی اطلاعات | حساسیت به مسئله | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشکی | متصدیان پذیرش و منشی‌های بخش پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | داروسازان | دستیاران و کمک‌کارکنان داروخانه | تکنسین‌های خون‌گیری (خون‌گیرها)</t>
+          <t>بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | داروسازان | کمک‌متصدیان داروخانه | کارشناسان و تکنسین‌های خون‌گیری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره‌گری | خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران بالینی پیشرفته روان‌پزشکی | روان‌شناسان بالینی و مشاور | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | کاردرمانگران | بهیاران و کمک‌مراقبان بخش روان‌پزشکی | روان‌پزشکان</t>
+          <t>پرستاران تخصصی روانپزشکی | روان‌شناسان بالینی و مشاوران سلامت روان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کاردرمانگران | کمک‌یاران بخش روان‌پزشکی | روان‌پزشکان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | استراتژی‌های یادگیری | یادگیری فعال | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | ثبات دست و بازو | چابکی دستی | توجه انتخابی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | ثبات دست و بازو | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دستیاران بیهوشی | تکنسین‌های فوریت‌های پزشکی | آماده‌سازان تجهیزات پزشکی | پرستاران بیهوشی | جراحان ارتوپد، به‌جز اطفال | جراحان کودکان | دستیاران جراحی</t>
+          <t>دستیاران متخصص بیهوشی | تکنسین‌های فوریت‌های پزشکی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | پرستاران بیهوشی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
